--- a/public/data/bios.xlsx
+++ b/public/data/bios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sufi-bios\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C16CCC-3B27-4A09-BB6B-F5D1C2C4357C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C46D6B-7C22-4DFB-A2DD-B7FD51803498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="1260" windowWidth="32895" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24150" yWindow="1425" windowWidth="26025" windowHeight="19305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5543,9 +5543,6 @@
     <t>Abū Muḥammad al-Jarīrī</t>
   </si>
   <si>
-    <t>Abū al-Ḥasan Bannān al-Ḥammāl</t>
-  </si>
-  <si>
     <t>Abū Ḥamzah al-Baghdādī</t>
   </si>
   <si>
@@ -6726,6 +6723,9 @@
   </si>
   <si>
     <t>count</t>
+  </si>
+  <si>
+    <t>Abū al-Ḥasan Bunān al-Ḥammāl</t>
   </si>
 </sst>
 </file>
@@ -7091,7 +7091,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -7102,7 +7102,7 @@
         <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="D2" t="s">
         <v>200</v>
@@ -7201,7 +7201,7 @@
         <v>435</v>
       </c>
       <c r="C5" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="D5" t="s">
         <v>177</v>
@@ -7234,7 +7234,7 @@
         <v>1626</v>
       </c>
       <c r="C6" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D6" t="s">
         <v>228</v>
@@ -7267,7 +7267,7 @@
         <v>1625</v>
       </c>
       <c r="C7" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="D7" t="s">
         <v>456</v>
@@ -7366,7 +7366,7 @@
         <v>1609</v>
       </c>
       <c r="C10" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="D10" t="s">
         <v>371</v>
@@ -7399,7 +7399,7 @@
         <v>1643</v>
       </c>
       <c r="C11" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="D11" t="s">
         <v>774</v>
@@ -7432,7 +7432,7 @@
         <v>1725</v>
       </c>
       <c r="C12" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="D12" t="s">
         <v>775</v>
@@ -7465,7 +7465,7 @@
         <v>1603</v>
       </c>
       <c r="C13" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="D13" t="s">
         <v>327</v>
@@ -7762,7 +7762,7 @@
         <v>1750</v>
       </c>
       <c r="C22" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -7861,7 +7861,7 @@
         <v>1460</v>
       </c>
       <c r="C25" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="D25" t="s">
         <v>55</v>
@@ -7894,7 +7894,7 @@
         <v>1792</v>
       </c>
       <c r="C26" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="D26" t="s">
         <v>286</v>
@@ -7927,7 +7927,7 @@
         <v>1703</v>
       </c>
       <c r="C27" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="D27" t="s">
         <v>937</v>
@@ -7960,7 +7960,7 @@
         <v>1705</v>
       </c>
       <c r="C28" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="D28" t="s">
         <v>557</v>
@@ -8092,7 +8092,7 @@
         <v>1776</v>
       </c>
       <c r="C32" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
@@ -8158,7 +8158,7 @@
         <v>742</v>
       </c>
       <c r="C34" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="D34" t="s">
         <v>190</v>
@@ -8191,7 +8191,7 @@
         <v>1807</v>
       </c>
       <c r="C35" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="D35" t="s">
         <v>268</v>
@@ -8224,7 +8224,7 @@
         <v>1722</v>
       </c>
       <c r="C36" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="D36" t="s">
         <v>747</v>
@@ -8257,7 +8257,7 @@
         <v>1747</v>
       </c>
       <c r="C37" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="D37" t="s">
         <v>824</v>
@@ -8323,7 +8323,7 @@
         <v>914</v>
       </c>
       <c r="C39" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="D39" t="s">
         <v>669</v>
@@ -8356,7 +8356,7 @@
         <v>943</v>
       </c>
       <c r="C40" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="D40" t="s">
         <v>615</v>
@@ -8422,7 +8422,7 @@
         <v>1762</v>
       </c>
       <c r="C42" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="D42" t="s">
         <v>113</v>
@@ -8455,7 +8455,7 @@
         <v>1782</v>
       </c>
       <c r="C43" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="D43" t="s">
         <v>469</v>
@@ -8554,7 +8554,7 @@
         <v>1173</v>
       </c>
       <c r="C46" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="D46" t="s">
         <v>228</v>
@@ -8770,7 +8770,7 @@
         <v>1738</v>
       </c>
       <c r="C53" t="s">
-        <v>1834</v>
+        <v>2228</v>
       </c>
       <c r="D53" t="s">
         <v>763</v>
@@ -8800,7 +8800,7 @@
         <v>1055</v>
       </c>
       <c r="C54" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="D54" t="s">
         <v>806</v>
@@ -8830,7 +8830,7 @@
         <v>491</v>
       </c>
       <c r="C55" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="D55" t="s">
         <v>492</v>
@@ -8860,7 +8860,7 @@
         <v>1809</v>
       </c>
       <c r="C56" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="D56" t="s">
         <v>492</v>
@@ -8890,7 +8890,7 @@
         <v>523</v>
       </c>
       <c r="C57" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="D57" t="s">
         <v>463</v>
@@ -8920,7 +8920,7 @@
         <v>1650</v>
       </c>
       <c r="C58" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="E58" t="s">
         <v>512</v>
@@ -8950,7 +8950,7 @@
         <v>1605</v>
       </c>
       <c r="C59" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="D59">
         <v>363</v>
@@ -9010,7 +9010,7 @@
         <v>1461</v>
       </c>
       <c r="C61" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -9040,7 +9040,7 @@
         <v>1677</v>
       </c>
       <c r="C62" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E62" t="s">
         <v>547</v>
@@ -9070,7 +9070,7 @@
         <v>1676</v>
       </c>
       <c r="C63" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E63" t="s">
         <v>140</v>
@@ -9100,7 +9100,7 @@
         <v>1682</v>
       </c>
       <c r="C64" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="D64" t="s">
         <v>651</v>
@@ -9160,7 +9160,7 @@
         <v>1697</v>
       </c>
       <c r="C66" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="E66" t="s">
         <v>403</v>
@@ -9220,7 +9220,7 @@
         <v>1698</v>
       </c>
       <c r="C68" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="D68" t="s">
         <v>463</v>
@@ -9250,7 +9250,7 @@
         <v>1704</v>
       </c>
       <c r="C69" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="E69" t="s">
         <v>246</v>
@@ -9310,7 +9310,7 @@
         <v>1765</v>
       </c>
       <c r="C71" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="E71" t="s">
         <v>455</v>
@@ -9340,7 +9340,7 @@
         <v>1819</v>
       </c>
       <c r="C72" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="E72" t="s">
         <v>177</v>
@@ -9400,7 +9400,7 @@
         <v>1775</v>
       </c>
       <c r="C74" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="D74" t="s">
         <v>158</v>
@@ -9430,7 +9430,7 @@
         <v>1772</v>
       </c>
       <c r="C75" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="E75" t="s">
         <v>210</v>
@@ -9580,7 +9580,7 @@
         <v>1735</v>
       </c>
       <c r="C80" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="E80" t="s">
         <v>661</v>
@@ -9697,10 +9697,10 @@
         <v>807</v>
       </c>
       <c r="B84" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="C84" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="D84">
         <v>360</v>
@@ -9790,7 +9790,7 @@
         <v>462</v>
       </c>
       <c r="C87" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E87">
         <v>382</v>
@@ -9817,7 +9817,7 @@
         <v>1740</v>
       </c>
       <c r="C88" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="E88" t="s">
         <v>807</v>
@@ -9925,7 +9925,7 @@
         <v>610</v>
       </c>
       <c r="C92" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="E92" t="s">
         <v>583</v>
@@ -9952,7 +9952,7 @@
         <v>1663</v>
       </c>
       <c r="C93" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="E93" t="s">
         <v>611</v>
@@ -9979,7 +9979,7 @@
         <v>1664</v>
       </c>
       <c r="C94" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="E94" t="s">
         <v>264</v>
@@ -10033,7 +10033,7 @@
         <v>1691</v>
       </c>
       <c r="C96" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="E96" t="s">
         <v>218</v>
@@ -10060,7 +10060,7 @@
         <v>1693</v>
       </c>
       <c r="C97" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E97" t="s">
         <v>339</v>
@@ -10087,7 +10087,7 @@
         <v>1695</v>
       </c>
       <c r="C98" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="D98" t="s">
         <v>668</v>
@@ -10114,7 +10114,7 @@
         <v>1711</v>
       </c>
       <c r="C99" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="E99" t="s">
         <v>272</v>
@@ -10168,7 +10168,7 @@
         <v>1771</v>
       </c>
       <c r="C101" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="E101">
         <v>288</v>
@@ -10195,7 +10195,7 @@
         <v>1233</v>
       </c>
       <c r="C102" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="F102" t="s">
         <v>432</v>
@@ -10222,7 +10222,7 @@
         <v>1142</v>
       </c>
       <c r="C103" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="D103" t="s">
         <v>98</v>
@@ -10249,7 +10249,7 @@
         <v>1619</v>
       </c>
       <c r="C104" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="D104" t="s">
         <v>328</v>
@@ -10273,7 +10273,7 @@
         <v>1648</v>
       </c>
       <c r="C105" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="F105" t="s">
         <v>550</v>
@@ -10297,7 +10297,7 @@
         <v>1467</v>
       </c>
       <c r="C106" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="F106" t="s">
         <v>99</v>
@@ -10441,7 +10441,7 @@
         <v>1701</v>
       </c>
       <c r="C112" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="F112" t="s">
         <v>669</v>
@@ -10465,7 +10465,7 @@
         <v>1707</v>
       </c>
       <c r="C113" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="F113" t="s">
         <v>181</v>
@@ -10489,7 +10489,7 @@
         <v>1709</v>
       </c>
       <c r="C114" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="E114" t="s">
         <v>184</v>
@@ -10513,7 +10513,7 @@
         <v>1710</v>
       </c>
       <c r="C115" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="E115" t="s">
         <v>728</v>
@@ -10537,7 +10537,7 @@
         <v>732</v>
       </c>
       <c r="C116" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="D116" t="s">
         <v>360</v>
@@ -10585,7 +10585,7 @@
         <v>1686</v>
       </c>
       <c r="C118" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="G118" t="s">
         <v>502</v>
@@ -10609,7 +10609,7 @@
         <v>1407</v>
       </c>
       <c r="C119" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="F119" t="s">
         <v>754</v>
@@ -10657,7 +10657,7 @@
         <v>1075</v>
       </c>
       <c r="C121" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="F121" t="s">
         <v>1076</v>
@@ -10681,7 +10681,7 @@
         <v>1794</v>
       </c>
       <c r="C122" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="D122" t="s">
         <v>12</v>
@@ -10705,7 +10705,7 @@
         <v>1795</v>
       </c>
       <c r="C123" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="D123" t="s">
         <v>388</v>
@@ -10729,7 +10729,7 @@
         <v>1806</v>
       </c>
       <c r="C124" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="F124" t="s">
         <v>1205</v>
@@ -10753,7 +10753,7 @@
         <v>1245</v>
       </c>
       <c r="C125" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="F125" t="s">
         <v>23</v>
@@ -10774,7 +10774,7 @@
         <v>1768</v>
       </c>
       <c r="C126" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="F126" t="s">
         <v>343</v>
@@ -10816,7 +10816,7 @@
         <v>1616</v>
       </c>
       <c r="C128" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F128" t="s">
         <v>9</v>
@@ -10900,7 +10900,7 @@
         <v>1462</v>
       </c>
       <c r="C132" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D132" t="s">
         <v>72</v>
@@ -10942,7 +10942,7 @@
         <v>1456</v>
       </c>
       <c r="C134" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F134" t="s">
         <v>37</v>
@@ -10963,7 +10963,7 @@
         <v>1623</v>
       </c>
       <c r="C135" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H135" t="s">
         <v>76</v>
@@ -10984,7 +10984,7 @@
         <v>1470</v>
       </c>
       <c r="C136" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="F136" t="s">
         <v>82</v>
@@ -11005,7 +11005,7 @@
         <v>1629</v>
       </c>
       <c r="C137" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H137" t="s">
         <v>479</v>
@@ -11026,7 +11026,7 @@
         <v>1634</v>
       </c>
       <c r="C138" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="F138" t="s">
         <v>90</v>
@@ -11047,7 +11047,7 @@
         <v>1630</v>
       </c>
       <c r="C139" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="F139" t="s">
         <v>481</v>
@@ -11068,7 +11068,7 @@
         <v>1624</v>
       </c>
       <c r="C140" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="F140" t="s">
         <v>454</v>
@@ -11089,7 +11089,7 @@
         <v>1631</v>
       </c>
       <c r="C141" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="F141" t="s">
         <v>467</v>
@@ -11131,7 +11131,7 @@
         <v>1464</v>
       </c>
       <c r="C143" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="F143" t="s">
         <v>80</v>
@@ -11215,7 +11215,7 @@
         <v>1472</v>
       </c>
       <c r="C147" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="F147" t="s">
         <v>88</v>
@@ -11236,7 +11236,7 @@
         <v>1636</v>
       </c>
       <c r="C148" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="F148" t="s">
         <v>92</v>
@@ -11257,7 +11257,7 @@
         <v>1283</v>
       </c>
       <c r="C149" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="F149" t="s">
         <v>94</v>
@@ -11278,7 +11278,7 @@
         <v>1644</v>
       </c>
       <c r="C150" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="F150" t="s">
         <v>532</v>
@@ -11299,7 +11299,7 @@
         <v>1474</v>
       </c>
       <c r="C151" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="F151" t="s">
         <v>99</v>
@@ -11320,7 +11320,7 @@
         <v>1473</v>
       </c>
       <c r="C152" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="F152" t="s">
         <v>95</v>
@@ -11341,7 +11341,7 @@
         <v>1465</v>
       </c>
       <c r="C153" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="F153" t="s">
         <v>95</v>
@@ -11362,7 +11362,7 @@
         <v>1466</v>
       </c>
       <c r="C154" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F154" t="s">
         <v>23</v>
@@ -11404,7 +11404,7 @@
         <v>1475</v>
       </c>
       <c r="C156" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="F156" t="s">
         <v>102</v>
@@ -11425,7 +11425,7 @@
         <v>1646</v>
       </c>
       <c r="C157" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F157" t="s">
         <v>526</v>
@@ -11509,7 +11509,7 @@
         <v>1657</v>
       </c>
       <c r="C161" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="F161" t="s">
         <v>127</v>
@@ -11530,7 +11530,7 @@
         <v>1660</v>
       </c>
       <c r="C162" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="F162" t="s">
         <v>137</v>
@@ -11551,7 +11551,7 @@
         <v>1661</v>
       </c>
       <c r="C163" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="F163" t="s">
         <v>139</v>
@@ -11572,7 +11572,7 @@
         <v>1665</v>
       </c>
       <c r="C164" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="F164" t="s">
         <v>144</v>
@@ -11593,7 +11593,7 @@
         <v>1658</v>
       </c>
       <c r="C165" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="F165" t="s">
         <v>53</v>
@@ -11635,7 +11635,7 @@
         <v>1488</v>
       </c>
       <c r="C167" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="F167" t="s">
         <v>121</v>
@@ -11656,7 +11656,7 @@
         <v>1495</v>
       </c>
       <c r="C168" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="F168" t="s">
         <v>134</v>
@@ -11677,7 +11677,7 @@
         <v>1497</v>
       </c>
       <c r="C169" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="F169" t="s">
         <v>140</v>
@@ -11698,7 +11698,7 @@
         <v>1667</v>
       </c>
       <c r="C170" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="F170" t="s">
         <v>146</v>
@@ -11719,7 +11719,7 @@
         <v>1500</v>
       </c>
       <c r="C171" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="F171" t="s">
         <v>139</v>
@@ -11761,7 +11761,7 @@
         <v>1669</v>
       </c>
       <c r="C173" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F173" t="s">
         <v>161</v>
@@ -11782,7 +11782,7 @@
         <v>1673</v>
       </c>
       <c r="C174" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="F174" t="s">
         <v>169</v>
@@ -11824,7 +11824,7 @@
         <v>1445</v>
       </c>
       <c r="C176" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -11845,7 +11845,7 @@
         <v>1674</v>
       </c>
       <c r="C177" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="F177">
         <v>93</v>
@@ -11866,7 +11866,7 @@
         <v>1683</v>
       </c>
       <c r="C178" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="H178" t="s">
         <v>194</v>
@@ -11887,7 +11887,7 @@
         <v>1514</v>
       </c>
       <c r="C179" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="F179" t="s">
         <v>203</v>
@@ -11908,7 +11908,7 @@
         <v>1745</v>
       </c>
       <c r="C180" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="F180" t="s">
         <v>815</v>
@@ -11929,7 +11929,7 @@
         <v>1521</v>
       </c>
       <c r="C181" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="F181" t="s">
         <v>213</v>
@@ -11992,7 +11992,7 @@
         <v>1808</v>
       </c>
       <c r="C184" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="F184" t="s">
         <v>212</v>
@@ -12013,7 +12013,7 @@
         <v>1692</v>
       </c>
       <c r="C185" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="F185" t="s">
         <v>223</v>
@@ -12034,7 +12034,7 @@
         <v>1694</v>
       </c>
       <c r="C186" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="F186" t="s">
         <v>225</v>
@@ -12055,7 +12055,7 @@
         <v>1531</v>
       </c>
       <c r="C187" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="F187" t="s">
         <v>244</v>
@@ -12076,7 +12076,7 @@
         <v>1675</v>
       </c>
       <c r="C188" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="F188" t="s">
         <v>184</v>
@@ -12097,7 +12097,7 @@
         <v>722</v>
       </c>
       <c r="C189" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="D189" t="s">
         <v>723</v>
@@ -12118,7 +12118,7 @@
         <v>1556</v>
       </c>
       <c r="C190" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="F190" t="s">
         <v>283</v>
@@ -12139,7 +12139,7 @@
         <v>1713</v>
       </c>
       <c r="C191" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H191" t="s">
         <v>287</v>
@@ -12181,7 +12181,7 @@
         <v>1718</v>
       </c>
       <c r="C193" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="F193" t="s">
         <v>295</v>
@@ -12202,7 +12202,7 @@
         <v>1734</v>
       </c>
       <c r="C194" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="F194" t="s">
         <v>202</v>
@@ -12244,7 +12244,7 @@
         <v>1733</v>
       </c>
       <c r="C196" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="F196" t="s">
         <v>238</v>
@@ -12265,7 +12265,7 @@
         <v>1729</v>
       </c>
       <c r="C197" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="F197" t="s">
         <v>303</v>
@@ -12328,7 +12328,7 @@
         <v>1577</v>
       </c>
       <c r="C200" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="F200" t="s">
         <v>120</v>
@@ -12349,7 +12349,7 @@
         <v>1284</v>
       </c>
       <c r="C201" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="F201" t="s">
         <v>790</v>
@@ -12391,7 +12391,7 @@
         <v>1256</v>
       </c>
       <c r="C203" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="F203" t="s">
         <v>423</v>
@@ -12433,7 +12433,7 @@
         <v>1278</v>
       </c>
       <c r="C205" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="F205" t="s">
         <v>322</v>
@@ -12475,7 +12475,7 @@
         <v>1751</v>
       </c>
       <c r="C207" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="F207" t="s">
         <v>300</v>
@@ -12496,7 +12496,7 @@
         <v>1239</v>
       </c>
       <c r="C208" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="F208" t="s">
         <v>405</v>
@@ -12517,7 +12517,7 @@
         <v>1276</v>
       </c>
       <c r="C209" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="F209" t="s">
         <v>884</v>
@@ -12559,7 +12559,7 @@
         <v>1250</v>
       </c>
       <c r="C211" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="F211" t="s">
         <v>83</v>
@@ -12601,7 +12601,7 @@
         <v>1764</v>
       </c>
       <c r="C213" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="F213" t="s">
         <v>609</v>
@@ -12622,7 +12622,7 @@
         <v>1249</v>
       </c>
       <c r="C214" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="F214" t="s">
         <v>691</v>
@@ -12643,7 +12643,7 @@
         <v>1565</v>
       </c>
       <c r="C215" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="F215" t="s">
         <v>18</v>
@@ -12664,7 +12664,7 @@
         <v>1241</v>
       </c>
       <c r="C216" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="F216" t="s">
         <v>996</v>
@@ -12685,7 +12685,7 @@
         <v>1774</v>
       </c>
       <c r="C217" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="D217" t="s">
         <v>897</v>
@@ -12706,7 +12706,7 @@
         <v>1773</v>
       </c>
       <c r="C218" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="F218" t="s">
         <v>1003</v>
@@ -12727,7 +12727,7 @@
         <v>1766</v>
       </c>
       <c r="C219" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="F219" t="s">
         <v>83</v>
@@ -12769,7 +12769,7 @@
         <v>1253</v>
       </c>
       <c r="C221" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="F221" t="s">
         <v>355</v>
@@ -12790,7 +12790,7 @@
         <v>1254</v>
       </c>
       <c r="C222" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="F222" t="s">
         <v>1006</v>
@@ -12811,7 +12811,7 @@
         <v>1783</v>
       </c>
       <c r="C223" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D223" t="s">
         <v>210</v>
@@ -12832,7 +12832,7 @@
         <v>1739</v>
       </c>
       <c r="C224" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="F224" t="s">
         <v>87</v>
@@ -12853,7 +12853,7 @@
         <v>1240</v>
       </c>
       <c r="C225" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F225" t="s">
         <v>141</v>
@@ -12895,7 +12895,7 @@
         <v>1791</v>
       </c>
       <c r="C227" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="F227" t="s">
         <v>75</v>
@@ -12916,7 +12916,7 @@
         <v>1264</v>
       </c>
       <c r="C228" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="F228" t="s">
         <v>1163</v>
@@ -12937,7 +12937,7 @@
         <v>1216</v>
       </c>
       <c r="C229" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="F229" t="s">
         <v>66</v>
@@ -12958,7 +12958,7 @@
         <v>1277</v>
       </c>
       <c r="C230" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="F230" t="s">
         <v>41</v>
@@ -12979,7 +12979,7 @@
         <v>1251</v>
       </c>
       <c r="C231" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="F231" t="s">
         <v>389</v>
@@ -13000,7 +13000,7 @@
         <v>1803</v>
       </c>
       <c r="C232" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="F232" t="s">
         <v>102</v>
@@ -13021,7 +13021,7 @@
         <v>1804</v>
       </c>
       <c r="C233" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="F233" t="s">
         <v>423</v>
@@ -13042,7 +13042,7 @@
         <v>1820</v>
       </c>
       <c r="C234" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="F234" t="s">
         <v>438</v>
@@ -13063,7 +13063,7 @@
         <v>1821</v>
       </c>
       <c r="C235" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F235" t="s">
         <v>394</v>
@@ -13123,7 +13123,7 @@
         <v>1700</v>
       </c>
       <c r="C238" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="I238" t="s">
         <v>234</v>
@@ -13159,7 +13159,7 @@
         <v>63</v>
       </c>
       <c r="C240" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="F240" t="s">
         <v>64</v>
@@ -13177,7 +13177,7 @@
         <v>70</v>
       </c>
       <c r="C241" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="D241" t="s">
         <v>71</v>
@@ -13195,7 +13195,7 @@
         <v>1297</v>
       </c>
       <c r="C242" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="I242" t="s">
         <v>314</v>
@@ -13249,7 +13249,7 @@
         <v>1604</v>
       </c>
       <c r="C245" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="D245" t="s">
         <v>18</v>
@@ -13321,7 +13321,7 @@
         <v>1761</v>
       </c>
       <c r="C249" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H249" t="s">
         <v>193</v>
@@ -13357,7 +13357,7 @@
         <v>1607</v>
       </c>
       <c r="C251" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D251" t="s">
         <v>199</v>
@@ -13375,7 +13375,7 @@
         <v>359</v>
       </c>
       <c r="C252" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="D252" t="s">
         <v>360</v>
@@ -13411,7 +13411,7 @@
         <v>370</v>
       </c>
       <c r="C254" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="D254" t="s">
         <v>23</v>
@@ -13429,7 +13429,7 @@
         <v>1610</v>
       </c>
       <c r="C255" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D255" t="s">
         <v>375</v>
@@ -13465,7 +13465,7 @@
         <v>1799</v>
       </c>
       <c r="C257" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="I257" t="s">
         <v>691</v>
@@ -13501,7 +13501,7 @@
         <v>1280</v>
       </c>
       <c r="C259" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="I259" t="s">
         <v>389</v>
@@ -13537,7 +13537,7 @@
         <v>1425</v>
       </c>
       <c r="C261" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="I261" t="s">
         <v>157</v>
@@ -13591,7 +13591,7 @@
         <v>1341</v>
       </c>
       <c r="C264" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="I264" t="s">
         <v>400</v>
@@ -13627,7 +13627,7 @@
         <v>1364</v>
       </c>
       <c r="C266" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="I266" t="s">
         <v>403</v>
@@ -13645,7 +13645,7 @@
         <v>1618</v>
       </c>
       <c r="C267" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="I267" t="s">
         <v>16</v>
@@ -13681,7 +13681,7 @@
         <v>1621</v>
       </c>
       <c r="C269" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="I269" t="s">
         <v>28</v>
@@ -13825,7 +13825,7 @@
         <v>1451</v>
       </c>
       <c r="C277" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="I277" t="s">
         <v>23</v>
@@ -13843,7 +13843,7 @@
         <v>1622</v>
       </c>
       <c r="C278" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="I278" t="s">
         <v>32</v>
@@ -13897,7 +13897,7 @@
         <v>1455</v>
       </c>
       <c r="C281" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="I281" t="s">
         <v>28</v>
@@ -13933,7 +13933,7 @@
         <v>1596</v>
       </c>
       <c r="C283" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="I283" t="s">
         <v>201</v>
@@ -13987,7 +13987,7 @@
         <v>1426</v>
       </c>
       <c r="C286" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="I286" t="s">
         <v>157</v>
@@ -14005,7 +14005,7 @@
         <v>1428</v>
       </c>
       <c r="C287" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="I287" t="s">
         <v>442</v>
@@ -14023,7 +14023,7 @@
         <v>443</v>
       </c>
       <c r="C288" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="I288" t="s">
         <v>444</v>
@@ -14041,7 +14041,7 @@
         <v>1422</v>
       </c>
       <c r="C289" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="I289" t="s">
         <v>444</v>
@@ -14059,7 +14059,7 @@
         <v>1423</v>
       </c>
       <c r="C290" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="I290" t="s">
         <v>444</v>
@@ -14095,7 +14095,7 @@
         <v>1430</v>
       </c>
       <c r="C292" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="F292" t="s">
         <v>445</v>
@@ -14167,7 +14167,7 @@
         <v>1463</v>
       </c>
       <c r="C296" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="F296" t="s">
         <v>79</v>
@@ -14239,7 +14239,7 @@
         <v>1763</v>
       </c>
       <c r="C300" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="D300" t="s">
         <v>684</v>
@@ -14257,7 +14257,7 @@
         <v>1810</v>
       </c>
       <c r="C301" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="F301" t="s">
         <v>64</v>
@@ -14275,7 +14275,7 @@
         <v>1633</v>
       </c>
       <c r="C302" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I302" t="s">
         <v>314</v>
@@ -14383,7 +14383,7 @@
         <v>1627</v>
       </c>
       <c r="C308" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="I308" t="s">
         <v>295</v>
@@ -14419,7 +14419,7 @@
         <v>1632</v>
       </c>
       <c r="C310" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="F310" t="s">
         <v>460</v>
@@ -14437,7 +14437,7 @@
         <v>1218</v>
       </c>
       <c r="C311" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="I311" t="s">
         <v>484</v>
@@ -14473,7 +14473,7 @@
         <v>1638</v>
       </c>
       <c r="C313" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="I313" t="s">
         <v>502</v>
@@ -14491,7 +14491,7 @@
         <v>1639</v>
       </c>
       <c r="C314" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="I314" t="s">
         <v>509</v>
@@ -14509,7 +14509,7 @@
         <v>1640</v>
       </c>
       <c r="C315" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="I315" t="s">
         <v>513</v>
@@ -14527,7 +14527,7 @@
         <v>1641</v>
       </c>
       <c r="C316" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="I316" t="s">
         <v>514</v>
@@ -14581,7 +14581,7 @@
         <v>1432</v>
       </c>
       <c r="C319" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="F319" t="s">
         <v>515</v>
@@ -14617,7 +14617,7 @@
         <v>517</v>
       </c>
       <c r="C321" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="I321" t="s">
         <v>121</v>
@@ -14653,7 +14653,7 @@
         <v>1642</v>
       </c>
       <c r="C323" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="I323" t="s">
         <v>206</v>
@@ -14779,7 +14779,7 @@
         <v>1796</v>
       </c>
       <c r="C330" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="F330" t="s">
         <v>790</v>
@@ -14797,7 +14797,7 @@
         <v>1645</v>
       </c>
       <c r="C331" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="I331" t="s">
         <v>535</v>
@@ -14833,7 +14833,7 @@
         <v>1385</v>
       </c>
       <c r="C333" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="I333" t="s">
         <v>538</v>
@@ -14887,7 +14887,7 @@
         <v>1295</v>
       </c>
       <c r="C336" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="I336" t="s">
         <v>50</v>
@@ -14959,7 +14959,7 @@
         <v>1647</v>
       </c>
       <c r="C340" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I340" t="s">
         <v>549</v>
@@ -14977,7 +14977,7 @@
         <v>1649</v>
       </c>
       <c r="C341" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="I341" t="s">
         <v>223</v>
@@ -14995,7 +14995,7 @@
         <v>1651</v>
       </c>
       <c r="C342" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="I342" t="s">
         <v>557</v>
@@ -15013,7 +15013,7 @@
         <v>1579</v>
       </c>
       <c r="C343" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="I343" t="s">
         <v>560</v>
@@ -15031,7 +15031,7 @@
         <v>1606</v>
       </c>
       <c r="C344" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="D344" t="s">
         <v>198</v>
@@ -15103,7 +15103,7 @@
         <v>1653</v>
       </c>
       <c r="C348" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="I348" t="s">
         <v>78</v>
@@ -15139,7 +15139,7 @@
         <v>1655</v>
       </c>
       <c r="C350" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="D350" t="s">
         <v>572</v>
@@ -15157,7 +15157,7 @@
         <v>1476</v>
       </c>
       <c r="C351" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="I351" t="s">
         <v>105</v>
@@ -15193,7 +15193,7 @@
         <v>1605</v>
       </c>
       <c r="C353" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="D353" t="s">
         <v>330</v>
@@ -15211,7 +15211,7 @@
         <v>1468</v>
       </c>
       <c r="C354" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="I354" t="s">
         <v>69</v>
@@ -15283,7 +15283,7 @@
         <v>1659</v>
       </c>
       <c r="C358" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="I358" t="s">
         <v>128</v>
@@ -15301,7 +15301,7 @@
         <v>1662</v>
       </c>
       <c r="C359" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="I359" t="s">
         <v>105</v>
@@ -15319,7 +15319,7 @@
         <v>1666</v>
       </c>
       <c r="C360" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="I360" t="s">
         <v>105</v>
@@ -15337,7 +15337,7 @@
         <v>1481</v>
       </c>
       <c r="C361" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="I361" t="s">
         <v>114</v>
@@ -15373,7 +15373,7 @@
         <v>1656</v>
       </c>
       <c r="C363" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="D363" t="s">
         <v>575</v>
@@ -15409,7 +15409,7 @@
         <v>1484</v>
       </c>
       <c r="C365" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="F365" t="s">
         <v>117</v>
@@ -15427,7 +15427,7 @@
         <v>1485</v>
       </c>
       <c r="C366" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="F366" t="s">
         <v>118</v>
@@ -15445,7 +15445,7 @@
         <v>1486</v>
       </c>
       <c r="C367" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="I367" t="s">
         <v>119</v>
@@ -15463,7 +15463,7 @@
         <v>1487</v>
       </c>
       <c r="C368" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="F368" t="s">
         <v>120</v>
@@ -15481,7 +15481,7 @@
         <v>1753</v>
       </c>
       <c r="C369" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="D369" t="s">
         <v>18</v>
@@ -15535,7 +15535,7 @@
         <v>1491</v>
       </c>
       <c r="C372" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="I372" t="s">
         <v>126</v>
@@ -15589,7 +15589,7 @@
         <v>1494</v>
       </c>
       <c r="C375" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="F375" t="s">
         <v>102</v>
@@ -15679,7 +15679,7 @@
         <v>1668</v>
       </c>
       <c r="C380" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="F380" t="s">
         <v>148</v>
@@ -15697,7 +15697,7 @@
         <v>1501</v>
       </c>
       <c r="C381" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="I381" t="s">
         <v>105</v>
@@ -15733,7 +15733,7 @@
         <v>1746</v>
       </c>
       <c r="C383" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="I383" t="s">
         <v>268</v>
@@ -15751,7 +15751,7 @@
         <v>1670</v>
       </c>
       <c r="C384" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="I384">
         <v>168</v>
@@ -15787,7 +15787,7 @@
         <v>627</v>
       </c>
       <c r="C386" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="D386" t="s">
         <v>628</v>
@@ -15877,7 +15877,7 @@
         <v>1504</v>
       </c>
       <c r="C391" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="I391" t="s">
         <v>163</v>
@@ -15913,7 +15913,7 @@
         <v>1507</v>
       </c>
       <c r="C393" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="F393" t="s">
         <v>161</v>
@@ -15967,7 +15967,7 @@
         <v>1817</v>
       </c>
       <c r="C396" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="D396" t="s">
         <v>234</v>
@@ -15985,7 +15985,7 @@
         <v>1678</v>
       </c>
       <c r="C397" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H397" t="s">
         <v>186</v>
@@ -16003,7 +16003,7 @@
         <v>1759</v>
       </c>
       <c r="C398" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="D398" t="s">
         <v>206</v>
@@ -16057,7 +16057,7 @@
         <v>1608</v>
       </c>
       <c r="C401" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D401" t="s">
         <v>363</v>
@@ -16111,7 +16111,7 @@
         <v>1681</v>
       </c>
       <c r="C404" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I404" t="s">
         <v>193</v>
@@ -16183,7 +16183,7 @@
         <v>1685</v>
       </c>
       <c r="C408" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="I408" t="s">
         <v>201</v>
@@ -16201,7 +16201,7 @@
         <v>1512</v>
       </c>
       <c r="C409" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="F409" t="s">
         <v>195</v>
@@ -16219,7 +16219,7 @@
         <v>1513</v>
       </c>
       <c r="C410" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="I410" t="s">
         <v>202</v>
@@ -16237,7 +16237,7 @@
         <v>1687</v>
       </c>
       <c r="C411" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="I411" t="s">
         <v>197</v>
@@ -16291,7 +16291,7 @@
         <v>1516</v>
       </c>
       <c r="C414" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I414" t="s">
         <v>206</v>
@@ -16309,7 +16309,7 @@
         <v>1744</v>
       </c>
       <c r="C415" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F415" t="s">
         <v>764</v>
@@ -16327,7 +16327,7 @@
         <v>1517</v>
       </c>
       <c r="C416" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="I416" t="s">
         <v>207</v>
@@ -16345,7 +16345,7 @@
         <v>1518</v>
       </c>
       <c r="C417" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="I417" t="s">
         <v>208</v>
@@ -16381,7 +16381,7 @@
         <v>1689</v>
       </c>
       <c r="C419" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="I419" t="s">
         <v>211</v>
@@ -16399,7 +16399,7 @@
         <v>1520</v>
       </c>
       <c r="C420" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="F420" t="s">
         <v>212</v>
@@ -16507,7 +16507,7 @@
         <v>1525</v>
       </c>
       <c r="C426" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="I426" t="s">
         <v>233</v>
@@ -16525,7 +16525,7 @@
         <v>1526</v>
       </c>
       <c r="C427" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="I427" t="s">
         <v>234</v>
@@ -16633,7 +16633,7 @@
         <v>1789</v>
       </c>
       <c r="C433" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="D433" t="s">
         <v>149</v>
@@ -16705,7 +16705,7 @@
         <v>1756</v>
       </c>
       <c r="C437" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D437" t="s">
         <v>647</v>
@@ -16723,7 +16723,7 @@
         <v>1532</v>
       </c>
       <c r="C438" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="I438" t="s">
         <v>9</v>
@@ -16741,7 +16741,7 @@
         <v>1708</v>
       </c>
       <c r="C439" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="I439" t="s">
         <v>253</v>
@@ -16759,7 +16759,7 @@
         <v>1533</v>
       </c>
       <c r="C440" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="I440" t="s">
         <v>251</v>
@@ -16795,7 +16795,7 @@
         <v>1706</v>
       </c>
       <c r="C442" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="I442" t="s">
         <v>253</v>
@@ -16813,7 +16813,7 @@
         <v>1534</v>
       </c>
       <c r="C443" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="I443" t="s">
         <v>201</v>
@@ -16939,7 +16939,7 @@
         <v>1541</v>
       </c>
       <c r="C450" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F450" t="s">
         <v>79</v>
@@ -16957,7 +16957,7 @@
         <v>1542</v>
       </c>
       <c r="C451" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="I451" t="s">
         <v>225</v>
@@ -16975,7 +16975,7 @@
         <v>1543</v>
       </c>
       <c r="C452" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F452" t="s">
         <v>145</v>
@@ -17029,7 +17029,7 @@
         <v>1545</v>
       </c>
       <c r="C455" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="I455" t="s">
         <v>263</v>
@@ -17047,7 +17047,7 @@
         <v>1546</v>
       </c>
       <c r="C456" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F456" t="s">
         <v>145</v>
@@ -17065,7 +17065,7 @@
         <v>721</v>
       </c>
       <c r="C457" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D457" t="s">
         <v>529</v>
@@ -17083,7 +17083,7 @@
         <v>724</v>
       </c>
       <c r="C458" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="D458" t="s">
         <v>725</v>
@@ -17209,7 +17209,7 @@
         <v>1712</v>
       </c>
       <c r="C465" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="I465" t="s">
         <v>278</v>
@@ -17227,7 +17227,7 @@
         <v>1788</v>
       </c>
       <c r="C466" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F466" t="s">
         <v>389</v>
@@ -17263,7 +17263,7 @@
         <v>1554</v>
       </c>
       <c r="C468" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="I468" t="s">
         <v>201</v>
@@ -17299,7 +17299,7 @@
         <v>1714</v>
       </c>
       <c r="C470" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="I470" t="s">
         <v>201</v>
@@ -17335,7 +17335,7 @@
         <v>1728</v>
       </c>
       <c r="C472" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="I472" t="s">
         <v>202</v>
@@ -17371,7 +17371,7 @@
         <v>1558</v>
       </c>
       <c r="C474" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="I474" t="s">
         <v>286</v>
@@ -17389,7 +17389,7 @@
         <v>1816</v>
       </c>
       <c r="C475" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="D475" t="s">
         <v>670</v>
@@ -17407,7 +17407,7 @@
         <v>1654</v>
       </c>
       <c r="C476" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="F476" t="s">
         <v>104</v>
@@ -17425,7 +17425,7 @@
         <v>1715</v>
       </c>
       <c r="C477" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="I477" t="s">
         <v>288</v>
@@ -17443,7 +17443,7 @@
         <v>1717</v>
       </c>
       <c r="C478" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="I478" t="s">
         <v>290</v>
@@ -17461,7 +17461,7 @@
         <v>1716</v>
       </c>
       <c r="C479" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="I479" t="s">
         <v>289</v>
@@ -17515,7 +17515,7 @@
         <v>1727</v>
       </c>
       <c r="C482" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="I482" t="s">
         <v>280</v>
@@ -17533,7 +17533,7 @@
         <v>1731</v>
       </c>
       <c r="C483" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="I483" t="s">
         <v>306</v>
@@ -17551,7 +17551,7 @@
         <v>1719</v>
       </c>
       <c r="C484" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="D484" t="s">
         <v>290</v>
@@ -17569,7 +17569,7 @@
         <v>1602</v>
       </c>
       <c r="C485" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="I485" t="s">
         <v>323</v>
@@ -17587,7 +17587,7 @@
         <v>1721</v>
       </c>
       <c r="C486" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="I486" t="s">
         <v>298</v>
@@ -17605,7 +17605,7 @@
         <v>1723</v>
       </c>
       <c r="C487" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="D487" t="s">
         <v>288</v>
@@ -17623,7 +17623,7 @@
         <v>1724</v>
       </c>
       <c r="C488" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="D488" t="s">
         <v>64</v>
@@ -17659,7 +17659,7 @@
         <v>1730</v>
       </c>
       <c r="C490" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="H490" t="s">
         <v>171</v>
@@ -17677,7 +17677,7 @@
         <v>760</v>
       </c>
       <c r="C491" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="D491" t="s">
         <v>162</v>
@@ -17767,7 +17767,7 @@
         <v>1574</v>
       </c>
       <c r="C496" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="I496" t="s">
         <v>302</v>
@@ -17803,7 +17803,7 @@
         <v>1576</v>
       </c>
       <c r="C498" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="I498" t="s">
         <v>305</v>
@@ -17839,7 +17839,7 @@
         <v>1592</v>
       </c>
       <c r="C500" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="I500" t="s">
         <v>308</v>
@@ -17893,7 +17893,7 @@
         <v>1595</v>
       </c>
       <c r="C503" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="I503" t="s">
         <v>313</v>
@@ -17929,7 +17929,7 @@
         <v>1601</v>
       </c>
       <c r="C505" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="I505" t="s">
         <v>322</v>
@@ -18001,7 +18001,7 @@
         <v>786</v>
       </c>
       <c r="C509" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="D509" t="s">
         <v>787</v>
@@ -18055,7 +18055,7 @@
         <v>1615</v>
       </c>
       <c r="C512" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H512" t="s">
         <v>407</v>
@@ -18127,7 +18127,7 @@
         <v>1327</v>
       </c>
       <c r="C516" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="I516" t="s">
         <v>797</v>
@@ -18145,7 +18145,7 @@
         <v>1736</v>
       </c>
       <c r="C517" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="D517" t="s">
         <v>289</v>
@@ -18163,7 +18163,7 @@
         <v>1236</v>
       </c>
       <c r="C518" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="I518" t="s">
         <v>800</v>
@@ -18181,7 +18181,7 @@
         <v>803</v>
       </c>
       <c r="C519" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="I519" t="s">
         <v>413</v>
@@ -18199,7 +18199,7 @@
         <v>1258</v>
       </c>
       <c r="C520" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="I520" t="s">
         <v>188</v>
@@ -18235,7 +18235,7 @@
         <v>805</v>
       </c>
       <c r="C522" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="I522" t="s">
         <v>316</v>
@@ -18253,7 +18253,7 @@
         <v>1743</v>
       </c>
       <c r="C523" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="I523" t="s">
         <v>811</v>
@@ -18307,7 +18307,7 @@
         <v>1419</v>
       </c>
       <c r="C526" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="I526" t="s">
         <v>688</v>
@@ -18343,7 +18343,7 @@
         <v>1418</v>
       </c>
       <c r="C528" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="I528" t="s">
         <v>283</v>
@@ -18397,7 +18397,7 @@
         <v>1427</v>
       </c>
       <c r="C531" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="I531" t="s">
         <v>157</v>
@@ -18415,7 +18415,7 @@
         <v>1421</v>
       </c>
       <c r="C532" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="I532" t="s">
         <v>181</v>
@@ -18433,7 +18433,7 @@
         <v>1424</v>
       </c>
       <c r="C533" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="I533" t="s">
         <v>444</v>
@@ -18451,7 +18451,7 @@
         <v>1376</v>
       </c>
       <c r="C534" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="I534" t="s">
         <v>241</v>
@@ -18469,7 +18469,7 @@
         <v>1611</v>
       </c>
       <c r="C535" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H535" t="s">
         <v>393</v>
@@ -18577,7 +18577,7 @@
         <v>1230</v>
       </c>
       <c r="C541" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="I541" t="s">
         <v>153</v>
@@ -18631,7 +18631,7 @@
         <v>1811</v>
       </c>
       <c r="C544" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="D544" t="s">
         <v>628</v>
@@ -18649,7 +18649,7 @@
         <v>1433</v>
       </c>
       <c r="C545" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H545" t="s">
         <v>623</v>
@@ -18703,7 +18703,7 @@
         <v>1749</v>
       </c>
       <c r="C548" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H548" t="s">
         <v>445</v>
@@ -18721,7 +18721,7 @@
         <v>1562</v>
       </c>
       <c r="C549" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="I549" t="s">
         <v>62</v>
@@ -18739,7 +18739,7 @@
         <v>1434</v>
       </c>
       <c r="C550" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="F550" t="s">
         <v>848</v>
@@ -18775,7 +18775,7 @@
         <v>1324</v>
       </c>
       <c r="C552" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="I552" t="s">
         <v>169</v>
@@ -18829,7 +18829,7 @@
         <v>1398</v>
       </c>
       <c r="C555" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="I555" t="s">
         <v>143</v>
@@ -18847,7 +18847,7 @@
         <v>1413</v>
       </c>
       <c r="C556" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I556" t="s">
         <v>854</v>
@@ -18901,7 +18901,7 @@
         <v>862</v>
       </c>
       <c r="C559" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F559" t="s">
         <v>143</v>
@@ -18919,7 +18919,7 @@
         <v>1752</v>
       </c>
       <c r="C560" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="D560" t="s">
         <v>744</v>
@@ -19099,7 +19099,7 @@
         <v>1315</v>
       </c>
       <c r="C570" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="I570" t="s">
         <v>806</v>
@@ -19135,7 +19135,7 @@
         <v>878</v>
       </c>
       <c r="C572" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="I572" t="s">
         <v>575</v>
@@ -19153,7 +19153,7 @@
         <v>1365</v>
       </c>
       <c r="C573" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="I573" t="s">
         <v>879</v>
@@ -19171,7 +19171,7 @@
         <v>1308</v>
       </c>
       <c r="C574" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="I574" t="s">
         <v>371</v>
@@ -19189,7 +19189,7 @@
         <v>1307</v>
       </c>
       <c r="C575" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="I575" t="s">
         <v>424</v>
@@ -19261,7 +19261,7 @@
         <v>1318</v>
       </c>
       <c r="C579" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="I579" t="s">
         <v>86</v>
@@ -19315,7 +19315,7 @@
         <v>1310</v>
       </c>
       <c r="C582" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="I582" t="s">
         <v>371</v>
@@ -19459,7 +19459,7 @@
         <v>1306</v>
       </c>
       <c r="C590" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="I590" t="s">
         <v>651</v>
@@ -19477,7 +19477,7 @@
         <v>1589</v>
       </c>
       <c r="C591" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="I591" t="s">
         <v>900</v>
@@ -19495,7 +19495,7 @@
         <v>1812</v>
       </c>
       <c r="C592" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="D592" t="s">
         <v>723</v>
@@ -19531,7 +19531,7 @@
         <v>1244</v>
       </c>
       <c r="C594" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="I594" t="s">
         <v>902</v>
@@ -19549,7 +19549,7 @@
         <v>1411</v>
       </c>
       <c r="C595" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I595" t="s">
         <v>908</v>
@@ -19585,7 +19585,7 @@
         <v>1338</v>
       </c>
       <c r="C597" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I597" t="s">
         <v>26</v>
@@ -19639,7 +19639,7 @@
         <v>917</v>
       </c>
       <c r="C600" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="I600" t="s">
         <v>88</v>
@@ -19675,7 +19675,7 @@
         <v>1754</v>
       </c>
       <c r="C602" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="D602" t="s">
         <v>326</v>
@@ -19693,7 +19693,7 @@
         <v>1755</v>
       </c>
       <c r="C603" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="I603" t="s">
         <v>250</v>
@@ -19711,7 +19711,7 @@
         <v>1247</v>
       </c>
       <c r="C604" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="I604" t="s">
         <v>250</v>
@@ -19729,7 +19729,7 @@
         <v>1813</v>
       </c>
       <c r="C605" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="D605" t="s">
         <v>101</v>
@@ -19801,7 +19801,7 @@
         <v>1390</v>
       </c>
       <c r="C609" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="I609" t="s">
         <v>926</v>
@@ -19873,7 +19873,7 @@
         <v>1757</v>
       </c>
       <c r="C613" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="D613" t="s">
         <v>210</v>
@@ -19891,7 +19891,7 @@
         <v>1758</v>
       </c>
       <c r="C614" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="H614" t="s">
         <v>938</v>
@@ -19945,7 +19945,7 @@
         <v>1392</v>
       </c>
       <c r="C617" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="I617" t="s">
         <v>148</v>
@@ -19999,7 +19999,7 @@
         <v>1814</v>
       </c>
       <c r="C620" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="D620" t="s">
         <v>71</v>
@@ -20143,7 +20143,7 @@
         <v>1281</v>
       </c>
       <c r="C628" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="F628" t="s">
         <v>963</v>
@@ -20233,7 +20233,7 @@
         <v>1352</v>
       </c>
       <c r="C633" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="I633" t="s">
         <v>67</v>
@@ -20305,7 +20305,7 @@
         <v>1785</v>
       </c>
       <c r="C637" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="I637" t="s">
         <v>306</v>
@@ -20323,7 +20323,7 @@
         <v>1291</v>
       </c>
       <c r="C638" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="I638" t="s">
         <v>211</v>
@@ -20395,7 +20395,7 @@
         <v>981</v>
       </c>
       <c r="C642" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="D642" t="s">
         <v>605</v>
@@ -20485,7 +20485,7 @@
         <v>1357</v>
       </c>
       <c r="C647" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="I647" t="s">
         <v>512</v>
@@ -20539,7 +20539,7 @@
         <v>1769</v>
       </c>
       <c r="C650" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="I650" t="s">
         <v>1001</v>
@@ -20593,7 +20593,7 @@
         <v>1770</v>
       </c>
       <c r="C653" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="I653" t="s">
         <v>789</v>
@@ -20629,7 +20629,7 @@
         <v>1777</v>
       </c>
       <c r="C655" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="H655" t="s">
         <v>151</v>
@@ -20755,7 +20755,7 @@
         <v>1344</v>
       </c>
       <c r="C662" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="I662" t="s">
         <v>583</v>
@@ -20881,7 +20881,7 @@
         <v>1317</v>
       </c>
       <c r="C669" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="I669" t="s">
         <v>199</v>
@@ -20899,7 +20899,7 @@
         <v>1436</v>
       </c>
       <c r="C670" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="F670" t="s">
         <v>481</v>
@@ -20917,7 +20917,7 @@
         <v>1028</v>
       </c>
       <c r="C671" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="H671" t="s">
         <v>278</v>
@@ -20953,7 +20953,7 @@
         <v>1030</v>
       </c>
       <c r="C673" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D673" t="s">
         <v>1031</v>
@@ -20971,7 +20971,7 @@
         <v>1032</v>
       </c>
       <c r="C674" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="I674" t="s">
         <v>930</v>
@@ -21115,7 +21115,7 @@
         <v>1046</v>
       </c>
       <c r="C682" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D682" t="s">
         <v>282</v>
@@ -21151,7 +21151,7 @@
         <v>1238</v>
       </c>
       <c r="C684" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="I684" t="s">
         <v>160</v>
@@ -21187,7 +21187,7 @@
         <v>1781</v>
       </c>
       <c r="C686" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="D686" t="s">
         <v>206</v>
@@ -21205,7 +21205,7 @@
         <v>1051</v>
       </c>
       <c r="C687" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="D687" t="s">
         <v>197</v>
@@ -21223,7 +21223,7 @@
         <v>1270</v>
       </c>
       <c r="C688" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="I688" t="s">
         <v>937</v>
@@ -21241,7 +21241,7 @@
         <v>1296</v>
       </c>
       <c r="C689" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="I689" t="s">
         <v>1058</v>
@@ -21331,7 +21331,7 @@
         <v>1437</v>
       </c>
       <c r="C694" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="F694" t="s">
         <v>30</v>
@@ -21349,7 +21349,7 @@
         <v>1282</v>
       </c>
       <c r="C695" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="I695" t="s">
         <v>89</v>
@@ -21367,7 +21367,7 @@
         <v>1815</v>
       </c>
       <c r="C696" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="D696" t="s">
         <v>1031</v>
@@ -21421,7 +21421,7 @@
         <v>1325</v>
       </c>
       <c r="C699" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I699" t="s">
         <v>169</v>
@@ -21475,7 +21475,7 @@
         <v>1260</v>
       </c>
       <c r="C702" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="I702" t="s">
         <v>529</v>
@@ -21511,7 +21511,7 @@
         <v>1415</v>
       </c>
       <c r="C704" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="I704" t="s">
         <v>94</v>
@@ -21637,7 +21637,7 @@
         <v>1566</v>
       </c>
       <c r="C711" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="I711" t="s">
         <v>596</v>
@@ -21655,7 +21655,7 @@
         <v>1567</v>
       </c>
       <c r="C712" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="I712" t="s">
         <v>146</v>
@@ -21745,7 +21745,7 @@
         <v>1569</v>
       </c>
       <c r="C717" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="I717" t="s">
         <v>392</v>
@@ -21799,7 +21799,7 @@
         <v>1314</v>
       </c>
       <c r="C720" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="I720" t="s">
         <v>463</v>
@@ -21817,7 +21817,7 @@
         <v>1093</v>
       </c>
       <c r="C721" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="I721" t="s">
         <v>575</v>
@@ -21871,7 +21871,7 @@
         <v>1591</v>
       </c>
       <c r="C724" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="I724" t="s">
         <v>282</v>
@@ -21889,7 +21889,7 @@
         <v>1412</v>
       </c>
       <c r="C725" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="I725" t="s">
         <v>908</v>
@@ -21943,7 +21943,7 @@
         <v>1246</v>
       </c>
       <c r="C728" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="I728" t="s">
         <v>48</v>
@@ -21997,7 +21997,7 @@
         <v>1438</v>
       </c>
       <c r="C731" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F731" t="s">
         <v>104</v>
@@ -22069,7 +22069,7 @@
         <v>1108</v>
       </c>
       <c r="C735" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="H735" t="s">
         <v>800</v>
@@ -22141,7 +22141,7 @@
         <v>1612</v>
       </c>
       <c r="C739" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="H739" t="s">
         <v>395</v>
@@ -22285,7 +22285,7 @@
         <v>1599</v>
       </c>
       <c r="C747" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="F747" t="s">
         <v>441</v>
@@ -22321,7 +22321,7 @@
         <v>1135</v>
       </c>
       <c r="C749" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="G749" t="s">
         <v>53</v>
@@ -22339,7 +22339,7 @@
         <v>1326</v>
       </c>
       <c r="C750" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="I750" t="s">
         <v>169</v>
@@ -22375,7 +22375,7 @@
         <v>1787</v>
       </c>
       <c r="C752" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="D752" t="s">
         <v>414</v>
@@ -22429,7 +22429,7 @@
         <v>1303</v>
       </c>
       <c r="C755" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="I755" t="s">
         <v>65</v>
@@ -22483,7 +22483,7 @@
         <v>1793</v>
       </c>
       <c r="C758" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="D758" t="s">
         <v>206</v>
@@ -22573,7 +22573,7 @@
         <v>1221</v>
       </c>
       <c r="C763" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F763" t="s">
         <v>1154</v>
@@ -22663,7 +22663,7 @@
         <v>1408</v>
       </c>
       <c r="C768" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="I768" t="s">
         <v>1101</v>
@@ -22681,7 +22681,7 @@
         <v>1797</v>
       </c>
       <c r="C769" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="D769" t="s">
         <v>363</v>
@@ -22717,7 +22717,7 @@
         <v>1798</v>
       </c>
       <c r="C771" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="D771" t="s">
         <v>414</v>
@@ -22735,7 +22735,7 @@
         <v>1798</v>
       </c>
       <c r="C772" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="D772" t="s">
         <v>198</v>
@@ -22753,7 +22753,7 @@
         <v>1399</v>
       </c>
       <c r="C773" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="I773" t="s">
         <v>1161</v>
@@ -22771,7 +22771,7 @@
         <v>1410</v>
       </c>
       <c r="C774" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="I774" t="s">
         <v>88</v>
@@ -22843,7 +22843,7 @@
         <v>1171</v>
       </c>
       <c r="C778" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="I778" t="s">
         <v>1172</v>
@@ -22861,7 +22861,7 @@
         <v>1818</v>
       </c>
       <c r="C779" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="D779" t="s">
         <v>771</v>
@@ -22951,7 +22951,7 @@
         <v>1440</v>
       </c>
       <c r="C784" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F784" t="s">
         <v>1182</v>
@@ -23041,7 +23041,7 @@
         <v>1356</v>
       </c>
       <c r="C789" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="I789" t="s">
         <v>1187</v>
@@ -23059,7 +23059,7 @@
         <v>1800</v>
       </c>
       <c r="C790" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D790" t="s">
         <v>102</v>
@@ -23131,7 +23131,7 @@
         <v>1801</v>
       </c>
       <c r="C794" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I794" t="s">
         <v>1191</v>
@@ -23185,7 +23185,7 @@
         <v>1802</v>
       </c>
       <c r="C797" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="D797" t="s">
         <v>199</v>
@@ -23311,7 +23311,7 @@
         <v>1824</v>
       </c>
       <c r="C804" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="I804" t="s">
         <v>261</v>
@@ -23329,7 +23329,7 @@
         <v>1825</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="I805" t="s">
         <v>394</v>
@@ -23347,7 +23347,7 @@
         <v>1826</v>
       </c>
       <c r="C806" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="I806" t="s">
         <v>816</v>
@@ -23383,7 +23383,7 @@
         <v>1828</v>
       </c>
       <c r="C808" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="I808" t="s">
         <v>307</v>
@@ -23401,7 +23401,7 @@
         <v>1829</v>
       </c>
       <c r="C809" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="I809" t="s">
         <v>679</v>
@@ -23464,7 +23464,7 @@
         <v>1016</v>
       </c>
       <c r="C813" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="J813">
         <f t="shared" si="12"/>
